--- a/conf-data/excel/Datas/skill/skilleffect.xlsx
+++ b/conf-data/excel/Datas/skill/skilleffect.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="13065"/>
+    <workbookView windowWidth="27735" windowHeight="10140"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="2" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbBuff</t>
+    <t>buff.TbBuff</t>
   </si>
   <si>
     <t>Buff</t>
@@ -140,7 +140,7 @@
     <t>buff@skill/buff.xlsx</t>
   </si>
   <si>
-    <t>TbBuffEffect</t>
+    <t>buff.TbBuffEffect</t>
   </si>
   <si>
     <t>BuffEffect</t>
@@ -149,7 +149,7 @@
     <t>buffeffect@skill/buffeffect.xlsx</t>
   </si>
   <si>
-    <t>TbBuffCond</t>
+    <t>buff.TbBuffCond</t>
   </si>
   <si>
     <t>BuffCond</t>
@@ -158,7 +158,7 @@
     <t>condition@skill/buffcond.xlsx</t>
   </si>
   <si>
-    <t>TbAbnormalNeedCond</t>
+    <t>buff.TbAbnormalNeedCond</t>
   </si>
   <si>
     <t>AbnormalNeedCond</t>
@@ -1791,10 +1791,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1827,59 +1827,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1895,11 +1843,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1913,23 +1903,33 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1942,10 +1942,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2019,7 +2019,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2031,7 +2085,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2043,7 +2139,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2055,49 +2157,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2109,73 +2169,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2219,7 +2219,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2242,8 +2242,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2263,6 +2272,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2277,30 +2301,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2309,10 +2309,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2321,7 +2321,7 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2330,7 +2330,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2339,115 +2339,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
